--- a/stories/arbres/TREE-SAN-058.xlsx
+++ b/stories/arbres/TREE-SAN-058.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Jules est avec papa, à la ferme. Jules a envie de jouer. papa est là, tout près. On va apprendre : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules écoute papa. Jules entend les mots : mouchoir, poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Jules respire. Jules retient : mouchoir, poubelle. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2230,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2539,6 +2592,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2701,6 +2759,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2863,6 +2926,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3025,6 +3093,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3187,6 +3260,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3349,6 +3427,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3511,6 +3594,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3673,6 +3761,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3863,6 +3956,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4025,6 +4123,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4187,6 +4290,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4349,6 +4457,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4511,6 +4624,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4673,6 +4791,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4835,6 +4958,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4997,6 +5125,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5187,6 +5320,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5349,6 +5487,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5511,6 +5654,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5673,6 +5821,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5835,6 +5988,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5997,6 +6155,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6159,6 +6322,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6183,7 +6351,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On montre du doigt, sans courir. papa dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6321,6 +6489,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On montre du doigt, sans courir.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Jules respire. Jules retient : mouchoir, poubelle. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6855,6 +7039,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7017,6 +7206,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7207,6 +7401,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7369,6 +7568,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7531,6 +7735,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7693,6 +7902,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7855,6 +8069,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8017,6 +8236,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8179,6 +8403,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8341,6 +8570,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8531,6 +8765,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8693,6 +8932,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8855,6 +9099,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9017,6 +9266,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9179,6 +9433,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9341,6 +9600,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9503,6 +9767,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9665,6 +9934,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9855,6 +10129,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10017,6 +10296,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10179,6 +10463,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10341,6 +10630,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10503,6 +10797,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10665,6 +10964,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10827,6 +11131,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10851,7 +11160,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Jules va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On rit un peu. papa dit : je suis là. On reste ensemble.</t>
+          <t>Jules va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10989,6 +11298,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Jules va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Jules se souvient : mouchoir, poubelle. Voici le geste : prendre un mouchoir ; jeter. On rit un peu.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Jules respire. Jules retient : mouchoir, poubelle. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11523,6 +11848,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11685,6 +12015,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11875,6 +12210,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12037,6 +12377,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12199,6 +12544,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12361,6 +12711,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12523,6 +12878,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12685,6 +13045,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. La lumière est claire. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12847,6 +13212,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13009,6 +13379,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tient la main. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13199,6 +13574,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13361,6 +13741,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13523,6 +13908,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13685,6 +14075,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13847,6 +14242,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14009,6 +14409,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14171,6 +14576,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14333,6 +14743,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On range un objet. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14523,6 +14938,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14685,6 +15105,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le matin. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14847,6 +15272,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15009,6 +15439,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint après la sieste. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15171,6 +15606,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15333,6 +15773,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le soir. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15495,6 +15940,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15513,7 +15963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15530,6 +15980,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-058.xlsx
+++ b/stories/arbres/TREE-SAN-058.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Jules est avec papa, à la ferme. Jules a envie de jouer. papa est là, tout près. On va apprendre : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules écoute papa. Jules entend les mots : mouchoir, poubelle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Jules respire. Jules retient : mouchoir, poubelle. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Jules a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2597,6 +2609,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2764,6 +2777,7 @@
           <t>narrateur|Jules rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2931,6 +2945,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3113,7 @@
           <t>narrateur|Jules rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3281,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3432,6 +3449,7 @@
           <t>narrateur|Jules rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la cuisine, les cubes et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3599,6 +3617,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3766,6 +3785,7 @@
           <t>narrateur|Jules a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3961,6 +3981,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4128,6 +4149,7 @@
           <t>narrateur|Jules rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4295,6 +4317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4462,6 +4485,7 @@
           <t>narrateur|Jules rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, le livre et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4629,6 +4653,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4796,6 +4821,7 @@
           <t>narrateur|Jules rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la cuisine, le livre et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4963,6 +4989,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5130,6 +5157,7 @@
           <t>narrateur|Jules a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5325,6 +5353,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5492,6 +5521,7 @@
           <t>narrateur|Jules rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5659,6 +5689,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5826,6 +5857,7 @@
           <t>narrateur|Jules rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5993,6 +6025,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6160,6 +6193,7 @@
           <t>narrateur|Jules rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la cuisine, la dînette et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6327,6 +6361,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6495,6 +6530,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Jules respire. Jules retient : mouchoir, poubelle. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7044,6 +7082,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7211,6 +7250,7 @@
           <t>narrateur|Jules a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7406,6 +7446,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7573,6 +7614,7 @@
           <t>narrateur|Jules rejoint le matin. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7740,6 +7782,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7907,6 +7950,7 @@
           <t>narrateur|Jules rejoint après la sieste. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de le jardin, les cubes et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8074,6 +8118,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8241,6 +8286,7 @@
           <t>narrateur|Jules rejoint le soir. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de le jardin, les cubes et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8408,6 +8454,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8575,6 +8622,7 @@
           <t>narrateur|Jules a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8770,6 +8818,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8937,6 +8986,7 @@
           <t>narrateur|Jules rejoint le matin. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9104,6 +9154,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9271,6 +9322,7 @@
           <t>narrateur|Jules rejoint après la sieste. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de le jardin, le livre et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9438,6 +9490,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9605,6 +9658,7 @@
           <t>narrateur|Jules rejoint le soir. La lumière est claire. On se tait une seconde. Cette fin-là est celle de le jardin, le livre et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9772,6 +9826,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9939,6 +9994,7 @@
           <t>narrateur|Jules a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10134,6 +10190,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10301,6 +10358,7 @@
           <t>narrateur|Jules rejoint le matin. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10468,6 +10526,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10635,6 +10694,7 @@
           <t>narrateur|Jules rejoint après la sieste. La lumière est claire. On rit un peu. Cette fin-là est celle de le jardin, la dînette et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10802,6 +10862,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10969,6 +11030,7 @@
           <t>narrateur|Jules rejoint le soir. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de le jardin, la dînette et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11136,6 +11198,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11304,6 +11367,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Se moucher.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : prendre un mouchoir ; jeter. Jules respire. Jules retient : mouchoir, poubelle. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11853,6 +11919,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12020,6 +12087,7 @@
           <t>narrateur|Jules a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12215,6 +12283,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12382,6 +12451,7 @@
           <t>narrateur|Jules rejoint le matin. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12549,6 +12619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12716,6 +12787,7 @@
           <t>narrateur|Jules rejoint après la sieste. Un vélo passe au loin. On se tait une seconde. Cette fin-là est celle de la chambre, les cubes et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12883,6 +12955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13050,6 +13123,7 @@
           <t>narrateur|Jules rejoint le soir. La lumière est claire. On se tient la main. Cette fin-là est celle de la chambre, les cubes et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13217,6 +13291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13384,6 +13459,7 @@
           <t>narrateur|Jules a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On se tient la main. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13579,6 +13655,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13746,6 +13823,7 @@
           <t>narrateur|Jules rejoint le matin. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13913,6 +13991,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14080,6 +14159,7 @@
           <t>narrateur|Jules rejoint après la sieste. La lumière est claire. On se tait une seconde. Cette fin-là est celle de la chambre, le livre et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14247,6 +14327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14414,6 +14495,7 @@
           <t>narrateur|Jules rejoint le soir. Il y a des miettes sur la table. On se tient la main. Cette fin-là est celle de la chambre, le livre et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14581,6 +14663,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14748,6 +14831,7 @@
           <t>narrateur|Jules a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre un mouchoir ; jeter. Jules répète tout bas : mouchoir, poubelle. On range un objet. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14943,6 +15027,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15110,6 +15195,7 @@
           <t>narrateur|Jules rejoint le matin. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le matin. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15277,6 +15363,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15444,6 +15531,7 @@
           <t>narrateur|Jules rejoint après la sieste. Il y a des miettes sur la table. On se tait une seconde. Cette fin-là est celle de la chambre, la dînette et après la sieste. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15611,6 +15699,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15778,6 +15867,7 @@
           <t>narrateur|Jules rejoint le soir. Un chat miaule une fois. On se tient la main. Cette fin-là est celle de la chambre, la dînette et le soir. Jules a appris : Se moucher. Voici le geste : prendre un mouchoir ; jeter. Jules a entendu : mouchoir, poubelle. Jules dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15945,6 +16035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15963,7 +16054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15987,6 +16078,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16001,7 +16106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16188,6 +16293,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
